--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133821886</v>
       </c>
       <c r="B2" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133821886</v>
       </c>
       <c r="B2" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133821886</v>
       </c>
       <c r="B2" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133821886</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133821886</v>
       </c>
       <c r="B2" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133821886</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133821886</v>
+        <v>134529373</v>
       </c>
       <c r="B2" t="n">
-        <v>79131</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Kangaslamm, Dlr</t>
+          <t>Barkberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497293</v>
+        <v>497179</v>
       </c>
       <c r="R2" t="n">
-        <v>6814038</v>
+        <v>6813685</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,15 +770,4565 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134529375</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497171</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6813738</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134529377</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497194</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6813791</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134529380</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497194</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6813817</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134529382</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497189</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6813827</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134529383</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497191</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6813854</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134529766</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497201</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6813849</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134529771</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497227</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6813872</v>
+      </c>
+      <c r="S9" t="n">
+        <v>57</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134529776</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497214</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6813918</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134529826</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>497290</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6814181</v>
+      </c>
+      <c r="S11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134529372</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497179</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6813685</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134529378</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497175</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6813790</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134529385</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497192</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6813869</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134529386</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497181</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6813879</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134529388</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497202</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6813908</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134529389</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497206</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6813942</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134529756</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497179</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6813728</v>
+      </c>
+      <c r="S18" t="n">
+        <v>32</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134529757</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>497205</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6813760</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134529758</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>497200</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6813803</v>
+      </c>
+      <c r="S20" t="n">
+        <v>29</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134529760</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>497180</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6813831</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134529761</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>497192</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6813840</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134529762</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>497198</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6813843</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134529763</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>497210</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6813840</v>
+      </c>
+      <c r="S24" t="n">
+        <v>51</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134529764</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>497218</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6813823</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134529765</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>497221</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6813823</v>
+      </c>
+      <c r="S26" t="n">
+        <v>30</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134529767</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>497201</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6813849</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134529768</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>497214</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6813839</v>
+      </c>
+      <c r="S28" t="n">
+        <v>24</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134529769</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>497220</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6813839</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134529770</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>497230</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6813850</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134529774</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>497196</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6813880</v>
+      </c>
+      <c r="S31" t="n">
+        <v>84</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134529775</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>497200</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6813943</v>
+      </c>
+      <c r="S32" t="n">
+        <v>32</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134529778</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>497252</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6813878</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134529823</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>497296</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6814223</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134529825</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>497297</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6814214</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134529376</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>497177</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6813741</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134529374</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>497176</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6813740</v>
+      </c>
+      <c r="S37" t="n">
+        <v>13</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134529379</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>497198</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6813790</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134529390</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>497244</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6813920</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134529777</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>497254</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6813866</v>
+      </c>
+      <c r="S40" t="n">
+        <v>11</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134529384</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>497185</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6813861</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134529391</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Barkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>497244</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6813921</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134529772</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>497204</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6813877</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133821886</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilla Kangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>497293</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6814038</v>
+      </c>
+      <c r="S44" t="n">
+        <v>50</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21630-2026 artfynd.xlsx
+++ b/artfynd/A 21630-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529373</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529375</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529377</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529380</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529382</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529383</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529766</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529776</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529826</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529372</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529378</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529385</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529386</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2313,6 +2388,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529388</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2420,6 +2500,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529389</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2527,6 +2612,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529756</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2634,6 +2724,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2741,6 +2836,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529758</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2848,6 +2948,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529760</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2955,6 +3060,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529761</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3062,6 +3172,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529762</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3169,6 +3284,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529763</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3276,6 +3396,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529764</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3383,6 +3508,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529765</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3490,6 +3620,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529767</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3597,6 +3732,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529768</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3704,6 +3844,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529769</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3811,6 +3956,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529770</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3918,6 +4068,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529774</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4025,6 +4180,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529775</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4132,6 +4292,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529778</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4239,6 +4404,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529823</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4346,6 +4516,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529825</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4453,6 +4628,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529376</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4560,6 +4740,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529374</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4667,6 +4852,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529379</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4774,6 +4964,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529390</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4891,6 +5086,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529777</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5003,6 +5203,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529384</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5120,6 +5325,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529391</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5232,6 +5442,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134529772</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5329,8 +5544,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133821886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>